--- a/1.training_model/supplementary/flowchart ML development.xlsx
+++ b/1.training_model/supplementary/flowchart ML development.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\1.training_model\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D09A7D9C-4E09-4EEE-84B8-49D561CCBE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D939A3F4-2454-4490-BA18-3D5CB84510E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A3A45E78-3C42-44AE-93A4-41B09245FE7F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>ALPHA_PREFIX_WEIGHT     = 0.65</t>
   </si>
@@ -51,6 +51,15 @@
   </si>
   <si>
     <t>TOP_K                   = 5</t>
+  </si>
+  <si>
+    <t>Result of model evaluation</t>
+  </si>
+  <si>
+    <t>Model Development</t>
+  </si>
+  <si>
+    <t>Model Application</t>
   </si>
 </sst>
 </file>
@@ -74,7 +83,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -84,6 +93,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -100,10 +115,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -127,7 +148,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>314655</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>181085</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2124622" cy="609013"/>
@@ -208,13 +229,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>160317</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>69747</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>163556</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>11741</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -267,7 +288,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>102798</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>178274</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1337221" cy="781240"/>
@@ -362,7 +383,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>198977</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>8566</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2336800" cy="515894"/>
@@ -439,7 +460,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>101763</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>174046</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1337221" cy="609013"/>
@@ -522,7 +543,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>407393</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>24229</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1944946" cy="436786"/>
@@ -603,7 +624,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>213129</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>979</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1445280" cy="264560"/>
@@ -677,13 +698,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>160317</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>169047</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>169467</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>2155</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -736,13 +757,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>168432</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>66218</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>169467</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>174046</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -795,13 +816,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>168432</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>65883</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>172806</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>27404</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -854,13 +875,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>317674</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>66502</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>410568</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>9429</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -910,7 +931,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>203326</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>6255</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1445280" cy="436786"/>
@@ -991,7 +1012,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>379604</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>17461</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1836574" cy="436786"/>
@@ -1069,13 +1090,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>540161</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>66503</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>87656</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>17461</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1125,13 +1146,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>317674</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>87628</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>333827</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>979</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1184,7 +1205,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>567293</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>159701</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1445280" cy="264560"/>
@@ -1258,13 +1279,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>76523</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>95659</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>87656</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>162876</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1317,13 +1338,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>333827</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>68848</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>76523</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>86245</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1375,14 +1396,14 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>145653</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>87570</xdr:rowOff>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>152645</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:colOff>150264</xdr:colOff>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>173264</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1400,8 +1421,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3171241" y="6004276"/>
-          <a:ext cx="6992" cy="623576"/>
+          <a:off x="3190875" y="6124575"/>
+          <a:ext cx="7389" cy="563789"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1434,7 +1455,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>37224</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>173264</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1445280" cy="264560"/>
@@ -1506,9 +1527,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>149246</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>17114</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1111383" cy="264560"/>
@@ -1575,15 +1596,15 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>97720</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>103080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>98172</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>68505</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1634,9 +1655,9 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>285314</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>13645</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2071535" cy="264560"/>
@@ -1708,9 +1729,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>457081</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>71680</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1711055" cy="462505"/>
@@ -1785,9 +1806,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>53181</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>20201</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1337221" cy="436786"/>
@@ -1883,15 +1904,15 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>98172</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>173822</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>106645</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>10470</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1942,15 +1963,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>106645</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>96436</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>111399</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>20201</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2001,9 +2022,9 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>68684</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>121946</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1337221" cy="436786"/>
@@ -2098,15 +2119,15 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>118173</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>102734</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>121207</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>125121</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2157,9 +2178,9 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>217053</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>20392</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2247541" cy="264560"/>
@@ -2231,15 +2252,15 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>111399</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>99799</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>129562</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>20392</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2290,9 +2311,9 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>233264</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>3580</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2247541" cy="264560"/>
@@ -2364,15 +2385,15 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>122515</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>20486</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>136999</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>6755</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2419,6 +2440,202 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>501650</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>48157</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>86087</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="165" name="Picture 164">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D054E631-581A-2DB1-A53F-DBD6EE80BD6E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1720850" y="14687550"/>
+          <a:ext cx="3810532" cy="2587987"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>511175</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>26862</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="166" name="Picture 165">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6CA9B8E-746F-EB0B-1F41-E8F195102B78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1730375" y="17649825"/>
+          <a:ext cx="3927475" cy="2468437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>105465</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>57699</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="167" name="Picture 166">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E9C45AF-C4DD-AB06-F5F7-EFF06E0B39A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1257300" y="8969375"/>
+          <a:ext cx="4940990" cy="3937549"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>358775</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1536</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="168" name="Picture 167">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE434843-A877-D2C5-6A5D-BA11AB0C2919}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4229100" y="2038350"/>
+          <a:ext cx="2225675" cy="858786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2741,41 +2958,73 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38AA77DD-8AB1-42B3-B673-04FA8231C115}">
-  <dimension ref="G6:AC12"/>
+  <dimension ref="B2:T49"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="12" max="12" width="2.1796875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="2.26953125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="7:29" x14ac:dyDescent="0.35">
-      <c r="AC6" t="s">
+    <row r="2" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="N2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="G15" s="1"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="H45" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="7:29" x14ac:dyDescent="0.35">
-      <c r="AC7" t="s">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="H46" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="7:29" x14ac:dyDescent="0.35">
-      <c r="AC8" t="s">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="H47" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="7:29" x14ac:dyDescent="0.35">
-      <c r="AC9" t="s">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="H48" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="7:29" x14ac:dyDescent="0.35">
-      <c r="AC10" t="s">
+    <row r="49" spans="8:8" x14ac:dyDescent="0.35">
+      <c r="H49" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="7:29" x14ac:dyDescent="0.35">
-      <c r="G12" s="1"/>
-    </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="N2:R2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
